--- a/daily_matches/job_matches_2026-08-28.xlsx
+++ b/daily_matches/job_matches_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Machine Learning and Artificial Intelligence Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>40</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43c47f699ab58bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=21760ea16a6f4c26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Job ID 3021796)</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, BigQuery, Data Lake, CI/CD, BigQuery, Tableau</t>
+          <t>LangChain, RAG, LLaMA, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7d2b2bb41cc0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Healthcare Engineer, Analytics Hub</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ECG Management Consultants</t>
+          <t>Ziff Davis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, Power BI</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b73be65e5b027154</t>
+          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Product Analytics Strategist</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf26ab72a3684cf</t>
+          <t>https://www.indeed.com/viewjob?jk=902e1bd2b4af48fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Product Analytics Strategist</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,172 +636,172 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8bd709e3bb8182</t>
+          <t>https://www.indeed.com/viewjob?jk=5872cc3072adbbbd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>New College Grad - Software Engineer</t>
+          <t>Senior Engineer 2, Merchandising (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Git, Snowflake, NoSQL, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfb93ed65fbd759</t>
+          <t>https://www.indeed.com/viewjob?jk=55921bc34dbfb58a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ab Initio Engineer</t>
+          <t>Engineer II, AI/ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de215cd633f0edb</t>
+          <t>https://www.indeed.com/viewjob?jk=6116f649bad11d58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist 3 - Freewheel</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, OpenCV, YOLO, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2f092305f59cae</t>
+          <t>https://www.indeed.com/viewjob?jk=262d552e5ef12f83</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
+          <t>AI Engineer - REMOTE USA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1c0a592c7badc3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc863149b0bb74</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Python AWS Software Engineer III (ML) - Agentic Treasury</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, CI/CD, Databricks, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb646be634c2c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE RunOps Engineer</t>
+          <t>Full Stack .NET Developer (AI Augmented Engineering)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Affinity Empowering Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, CI/CD, Git, Snowflake, Databricks, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec28a2f319417cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=887663a85634d317</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Hypothesis Testing</t>
+          <t>Data Scientist, MLflow, Docker, CI/CD, Terraform, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb87107aaaefb54</t>
+          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer, Model Pre-Training, Tesla AI</t>
+          <t>Sr. AI Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, AKS, Git, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,77 +916,1547 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da0dea936f0b4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=335ca012e2895d39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, GitHub Actions, Git, Snowflake, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f996476d3bbf762</t>
+          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, AI</t>
+          <t>AI/ML Engineer Precision Oncology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b2423173fa46d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer Precision Oncology</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Moffitt Cancer Center</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e03845e2a2128347</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Investigations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SpyCloud</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cdabd118b34d8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer — Agent Platform &amp; Document Intelligence</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FastAPI, Docker, CI/CD, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e82198d6a2f8dff</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Development Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Power Systems MFG., LLC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jupiter, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54be710cc09718e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Finance</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marlboro, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38276618e771db29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer Snowflake/Agentic AI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Valtech Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Terraform, Git, Snowflake, Databricks, Kafka, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ebf36281f9e5d65</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BluestoneLogic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99e1a2b867dd694a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Remote - Senior Software Engineer, Quality Engineering</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>arrivia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7af828bec73b455c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wag Walking</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd3044efad87fede</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f1efae92e327259</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AvKARE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d63c6f86f2a6d4a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GoDaddy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df16ca4465d6d1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer (Python / React)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3Pillar Global</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, Apache Airflow, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Engineer III, Site Reliability</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f36a226fa06534a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Product Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, S3, MLflow, Docker, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b2a83db6eaa907f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aderant</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c5de20fab19d55b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a573859b781997c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86eae7347b60946a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdc76bfb1722871e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=919084335ef0a807</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c765c181476494</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DIR OF SW SYSTEMS ENGINEERING -10378</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Extreme Networks</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e544a45d5b17ef84</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Enablement Intern</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, Kubernetes, Terraform, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d58f4016f25196ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer, AI Support</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Insurance Institute for Business and Home Safety</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Richburg, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f13dbc5a86d29348</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - Observability</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OnBoard</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Git, Python, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49f688aecd7e6ecf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Value Engineer, Consumer Packaged Goods (CPG)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, PyTorch, Git, Databricks, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da11394c4058fa74</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ae68f938e01621</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Apache Airflow, CI/CD, Terraform, Git, Snowflake, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26778131d9f5f29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GenAI Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21cf8eb2daebe321</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GenAI Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ddf4c1a1fe367ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Apache Airflow, CI/CD, Terraform, Git, Snowflake, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d7ae04df7a29c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Strategic Data &amp; Analytics Engineer (Cloud Data &amp; Agentic Infrastructure)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Shift Paradigm</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecd2844dc56e2cb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer — Conversational Voice AI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SmartAdvocate</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=074cdd71603e866c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Engineer (Fully Remote)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PadSplit</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, AKS, Terraform, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc610ffd09b5a2d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, Databricks, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c611edd102a53798</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Vehicle Mechatronic Embedded Controls</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Hadoop, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79e722d7847d7c6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Scientist - Decision Analytics</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b0b36645ea776b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Carbo Ceramics, LLC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dc690fe989d4301</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Engineer/Analyst – Data Historian System Administrator</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Southern Company</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f091892f73c1386a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior IT Applications Engineer - Java &amp; Cloud Technologies - Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f20089a196ab66c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Level III Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Blue Margin</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, Snowflake, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
         </is>
       </c>
     </row>
